--- a/artfynd/A 8257-2025 artfynd.xlsx
+++ b/artfynd/A 8257-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123750491</v>
       </c>
       <c r="B2" t="n">
-        <v>58165</v>
+        <v>58168</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>123750487</v>
       </c>
       <c r="B3" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 8257-2025 artfynd.xlsx
+++ b/artfynd/A 8257-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750491</v>
+        <v>123750487</v>
       </c>
       <c r="B2" t="n">
-        <v>58168</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750487</v>
+        <v>123750491</v>
       </c>
       <c r="B3" t="n">
-        <v>57643</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 8257-2025 artfynd.xlsx
+++ b/artfynd/A 8257-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750487</v>
+        <v>123750491</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750491</v>
+        <v>123750487</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 8257-2025 artfynd.xlsx
+++ b/artfynd/A 8257-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750491</v>
+        <v>123750487</v>
       </c>
       <c r="B2" t="n">
-        <v>58169</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750487</v>
+        <v>123750491</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 8257-2025 artfynd.xlsx
+++ b/artfynd/A 8257-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123750491</v>
+        <v>123750487</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -795,37 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123750487</v>
+        <v>123750491</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 8257-2025 artfynd.xlsx
+++ b/artfynd/A 8257-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123750487</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,8 +912,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123750491</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>